--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2022/LOUISIANA_2022.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2022/LOUISIANA_2022.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D750"/>
+  <dimension ref="A1:D744"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Asientos</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Calvillo</t>
@@ -421,9 +431,14 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pabellón de Arteaga</t>
+          <t>Pabellón De Arteaga</t>
         </is>
       </c>
       <c r="C5">
@@ -434,9 +449,14 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rincón de Romos</t>
+          <t>Rincón De Romos</t>
         </is>
       </c>
       <c r="C6">
@@ -447,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -478,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Mexicali</t>
@@ -491,9 +521,14 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Playas de Rosarito</t>
+          <t>Playas De Rosarito</t>
         </is>
       </c>
       <c r="C10">
@@ -504,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -517,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Total</t>
@@ -548,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Carmen</t>
@@ -561,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Champotón</t>
@@ -574,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Hopelchén</t>
@@ -587,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Total</t>
@@ -618,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Acapetahua</t>
@@ -631,9 +701,14 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Amatenango del Valle</t>
+          <t>Amatenango Del Valle</t>
         </is>
       </c>
       <c r="C20">
@@ -644,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Angel Albino Corzo</t>
@@ -657,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Arriaga</t>
@@ -670,9 +755,14 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Benemérito de las Américas</t>
+          <t>Benemérito De Las Américas</t>
         </is>
       </c>
       <c r="C23">
@@ -683,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Cacahoatán</t>
@@ -696,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Chamula</t>
@@ -709,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Chanal</t>
@@ -722,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Chicomuselo</t>
@@ -735,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Chilón</t>
@@ -748,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Cintalapa</t>
@@ -761,9 +881,14 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Comitán de Domínguez</t>
+          <t>Comitán De Domínguez</t>
         </is>
       </c>
       <c r="C30">
@@ -774,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Huehuetán</t>
@@ -787,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Huixtán</t>
@@ -800,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Huixtla</t>
@@ -813,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -826,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>La Concordia</t>
@@ -839,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -852,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -865,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -878,9 +1043,14 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Marqués de Comillas</t>
+          <t>Marqués De Comillas</t>
         </is>
       </c>
       <c r="C39">
@@ -891,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Mazatán</t>
@@ -904,9 +1079,14 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Montecristo de Guerrero</t>
+          <t>Montecristo De Guerrero</t>
         </is>
       </c>
       <c r="C41">
@@ -917,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Motozintla</t>
@@ -930,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Ocosingo</t>
@@ -943,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Ocotepec</t>
@@ -956,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ocozocoautla de Espinosa</t>
+          <t>Ocozocoautla De Espinosa</t>
         </is>
       </c>
       <c r="C45">
@@ -969,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Ostuacán</t>
@@ -982,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Palenque</t>
@@ -995,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Pijijiapan</t>
@@ -1008,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Pueblo Nuevo Solistahuacán</t>
@@ -1021,9 +1241,14 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Salto de Agua</t>
+          <t>Salto De Agua</t>
         </is>
       </c>
       <c r="C50">
@@ -1034,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Siltepec</t>
@@ -1047,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Suchiate</t>
@@ -1060,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -1073,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Tapalapa</t>
@@ -1086,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Tecpatán</t>
@@ -1099,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Tenejapa</t>
@@ -1112,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Tila</t>
@@ -1125,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -1138,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Tuxtla Chico</t>
@@ -1151,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Tuzantán</t>
@@ -1164,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Villa Comaltitlán</t>
@@ -1177,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Villa Corzo</t>
@@ -1190,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Villaflores</t>
@@ -1203,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1234,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Aldama</t>
@@ -1247,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Balleza</t>
@@ -1260,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Batopilas</t>
@@ -1273,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Camargo</t>
@@ -1286,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Chihuahua</t>
@@ -1299,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Chínipas</t>
@@ -1312,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1325,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Delicias</t>
@@ -1338,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Guachochi</t>
@@ -1351,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Guerrero</t>
@@ -1364,9 +1709,14 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C76">
@@ -1377,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -1390,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Madera</t>
@@ -1403,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Namiquipa</t>
@@ -1416,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Nuevo Casas Grandes</t>
@@ -1429,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Ojinaga</t>
@@ -1442,9 +1817,14 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>San Francisco del Oro</t>
+          <t>San Francisco Del Oro</t>
         </is>
       </c>
       <c r="C82">
@@ -1455,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Saucillo</t>
@@ -1468,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1499,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Allende</t>
@@ -1512,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Candela</t>
@@ -1525,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Francisco I. Madero</t>
@@ -1538,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Monclova</t>
@@ -1551,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Múzquiz</t>
@@ -1564,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Nava</t>
@@ -1577,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Piedras Negras</t>
@@ -1590,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Saltillo</t>
@@ -1603,9 +2033,14 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>San Juan de Sabinas</t>
+          <t>San Juan De Sabinas</t>
         </is>
       </c>
       <c r="C94">
@@ -1616,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>San Pedro</t>
@@ -1629,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Torreón</t>
@@ -1642,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Viesca</t>
@@ -1655,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Villa Unión</t>
@@ -1668,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1699,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Comala</t>
@@ -1712,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Manzanillo</t>
@@ -1725,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Tecomán</t>
@@ -1738,9 +2213,14 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Villa de Álvarez</t>
+          <t>Villa De Álvarez</t>
         </is>
       </c>
       <c r="C104">
@@ -1751,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1766,7 +2251,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -1782,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -1795,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -1808,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -1821,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1834,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -1847,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -1860,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -1873,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>La Magdalena Contreras</t>
@@ -1886,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -1899,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Milpa Alta</t>
@@ -1912,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Tláhuac</t>
@@ -1925,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -1938,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Xochimilco</t>
@@ -1951,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1982,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Durango</t>
@@ -1995,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Gómez Palacio</t>
@@ -2008,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -2021,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Guanaceví</t>
@@ -2034,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Lerdo</t>
@@ -2047,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Mezquital</t>
@@ -2060,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Nazas</t>
@@ -2073,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -2086,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Poanas</t>
@@ -2099,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Pueblo Nuevo</t>
@@ -2112,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Rodeo</t>
@@ -2125,6 +2735,11 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>San Dimas</t>
@@ -2138,9 +2753,14 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C134">
@@ -2151,9 +2771,14 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>San Pedro del Gallo</t>
+          <t>San Pedro Del Gallo</t>
         </is>
       </c>
       <c r="C135">
@@ -2164,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Santiago Papasquiaro</t>
@@ -2177,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -2190,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2205,12 +2845,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Acambay de Ruíz Castañeda</t>
+          <t>Acambay De Ruíz Castañeda</t>
         </is>
       </c>
       <c r="C139">
@@ -2221,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Acolman</t>
@@ -2234,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Aculco</t>
@@ -2247,9 +2897,14 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Almoloya de Alquisiras</t>
+          <t>Almoloya De Alquisiras</t>
         </is>
       </c>
       <c r="C142">
@@ -2260,6 +2915,11 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Amatepec</t>
@@ -2273,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Apaxco</t>
@@ -2286,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Atizapán</t>
@@ -2299,9 +2969,14 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Atizapán de Zaragoza</t>
+          <t>Atizapán De Zaragoza</t>
         </is>
       </c>
       <c r="C146">
@@ -2312,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Atlacomulco</t>
@@ -2325,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Capulhuac</t>
@@ -2338,6 +3023,11 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Chalco</t>
@@ -2351,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Chicoloapan</t>
@@ -2364,6 +3059,11 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>Chimalhuacán</t>
@@ -2377,6 +3077,11 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>Cuautitlán</t>
@@ -2390,9 +3095,14 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C153">
@@ -2403,6 +3113,11 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>El Oro</t>
@@ -2416,6 +3131,11 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>Jiquipilco</t>
@@ -2429,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Jocotitlán</t>
@@ -2442,6 +3167,11 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Metepec</t>
@@ -2455,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Morelos</t>
@@ -2468,9 +3203,14 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C159">
@@ -2481,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -2494,6 +3239,11 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>Nicolás Romero</t>
@@ -2507,9 +3257,14 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C162">
@@ -2520,9 +3275,14 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>San Simón de Guerrero</t>
+          <t>San Simón De Guerrero</t>
         </is>
       </c>
       <c r="C163">
@@ -2533,6 +3293,11 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>Sultepec</t>
@@ -2546,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Tecámac</t>
@@ -2559,6 +3329,11 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -2572,6 +3347,11 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>Temascalcingo</t>
@@ -2585,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Tenancingo</t>
@@ -2598,9 +3383,14 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Tenango del Valle</t>
+          <t>Tenango Del Valle</t>
         </is>
       </c>
       <c r="C169">
@@ -2611,9 +3401,14 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C170">
@@ -2624,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Tlatlaya</t>
@@ -2637,6 +3437,11 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -2650,6 +3455,11 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>Tonatico</t>
@@ -2663,9 +3473,14 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Valle de Bravo</t>
+          <t>Valle De Bravo</t>
         </is>
       </c>
       <c r="C174">
@@ -2676,6 +3491,11 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>Villa Guerrero</t>
@@ -2689,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Zacualpan</t>
@@ -2702,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2733,6 +3563,11 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>Acámbaro</t>
@@ -2746,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>Allende</t>
@@ -2759,9 +3599,14 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Apaseo el Alto</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C181">
@@ -2772,9 +3617,14 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Apaseo el Grande</t>
+          <t>Apaseo El Grande</t>
         </is>
       </c>
       <c r="C182">
@@ -2785,6 +3635,11 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -2798,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>Comonfort</t>
@@ -2811,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>Coroneo</t>
@@ -2824,6 +3689,11 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>Cortazar</t>
@@ -2837,6 +3707,11 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>Doctor Mora</t>
@@ -2850,9 +3725,14 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna de la Independencia Nacional</t>
+          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
         </is>
       </c>
       <c r="C188">
@@ -2863,6 +3743,11 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>Guanajuato</t>
@@ -2876,6 +3761,11 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -2889,6 +3779,11 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>Jerécuaro</t>
@@ -2902,6 +3797,11 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>León</t>
@@ -2915,6 +3815,11 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
           <t>Manuel Doblado</t>
@@ -2928,6 +3833,11 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>Moroleón</t>
@@ -2941,6 +3851,11 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -2954,6 +3869,11 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -2967,6 +3887,11 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>Pueblo Nuevo</t>
@@ -2980,6 +3905,11 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -2993,6 +3923,11 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -3006,9 +3941,14 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>San Diego de la Unión</t>
+          <t>San Diego De La Unión</t>
         </is>
       </c>
       <c r="C200">
@@ -3019,6 +3959,11 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
           <t>San Felipe</t>
@@ -3032,9 +3977,14 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>San Francisco del Rincón</t>
+          <t>San Francisco Del Rincón</t>
         </is>
       </c>
       <c r="C202">
@@ -3045,6 +3995,11 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>San José Iturbide</t>
@@ -3058,9 +4013,14 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>San Luis de la Paz</t>
+          <t>San Luis De La Paz</t>
         </is>
       </c>
       <c r="C204">
@@ -3071,9 +4031,14 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Santa Cruz de Juventino Rosas</t>
+          <t>Santa Cruz De Juventino Rosas</t>
         </is>
       </c>
       <c r="C205">
@@ -3084,9 +4049,14 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Silao de la Victoria</t>
+          <t>Silao De La Victoria</t>
         </is>
       </c>
       <c r="C206">
@@ -3097,6 +4067,11 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>Tarimoro</t>
@@ -3110,6 +4085,11 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -3123,6 +4103,11 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>Uriangato</t>
@@ -3136,9 +4121,14 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Valle de Santiago</t>
+          <t>Valle De Santiago</t>
         </is>
       </c>
       <c r="C210">
@@ -3149,6 +4139,11 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>Victoria</t>
@@ -3162,6 +4157,11 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
           <t>Villagrán</t>
@@ -3175,6 +4175,11 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>Xichú</t>
@@ -3188,6 +4193,11 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -3201,6 +4211,11 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3221,7 +4236,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C216">
@@ -3232,6 +4247,11 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
           <t>Apaxtla</t>
@@ -3245,6 +4265,11 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>Arcelia</t>
@@ -3258,6 +4283,11 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
           <t>Atlixtac</t>
@@ -3271,9 +4301,14 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Atoyac de Álvarez</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C220">
@@ -3284,9 +4319,14 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Ayutla de los Libres</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C221">
@@ -3297,9 +4337,14 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Buenavista de Cuéllar</t>
+          <t>Buenavista De Cuéllar</t>
         </is>
       </c>
       <c r="C222">
@@ -3310,9 +4355,14 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Chilapa de Álvarez</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C223">
@@ -3323,9 +4373,14 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C224">
@@ -3336,6 +4391,11 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>Copalillo</t>
@@ -3349,6 +4409,11 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>Copanatoyac</t>
@@ -3362,9 +4427,14 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Coyuca de Benítez</t>
+          <t>Coyuca De Benítez</t>
         </is>
       </c>
       <c r="C227">
@@ -3375,9 +4445,14 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Coyuca de Catalán</t>
+          <t>Coyuca De Catalán</t>
         </is>
       </c>
       <c r="C228">
@@ -3388,6 +4463,11 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>Cuajinicuilapa</t>
@@ -3401,9 +4481,14 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Cuetzala del Progreso</t>
+          <t>Cuetzala Del Progreso</t>
         </is>
       </c>
       <c r="C230">
@@ -3414,9 +4499,14 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Cutzamala de Pinzón</t>
+          <t>Cutzamala De Pinzón</t>
         </is>
       </c>
       <c r="C231">
@@ -3427,6 +4517,11 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
           <t>General Canuto A. Neri</t>
@@ -3440,6 +4535,11 @@
       </c>
     </row>
     <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
           <t>General Heliodoro Castillo</t>
@@ -3453,9 +4553,14 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Huitzuco de los Figueroa</t>
+          <t>Huitzuco De Los Figueroa</t>
         </is>
       </c>
       <c r="C234">
@@ -3466,9 +4571,14 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Iguala de la Independencia</t>
+          <t>Iguala De La Independencia</t>
         </is>
       </c>
       <c r="C235">
@@ -3479,9 +4589,14 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Zihuatanejo de Azueta</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C236">
@@ -3492,6 +4607,11 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>Juan R. Escudero</t>
@@ -3505,9 +4625,14 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>La Unión de Isidoro Montes de Oca</t>
+          <t>La Unión De Isidoro Montes De Oca</t>
         </is>
       </c>
       <c r="C238">
@@ -3518,6 +4643,11 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>Leonardo Bravo</t>
@@ -3531,6 +4661,11 @@
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>Malinaltepec</t>
@@ -3544,6 +4679,11 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>Metlatónoc</t>
@@ -3557,6 +4697,11 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>Ometepec</t>
@@ -3570,6 +4715,11 @@
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
           <t>Petatlán</t>
@@ -3583,6 +4733,11 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
           <t>Pungarabato</t>
@@ -3596,6 +4751,11 @@
       </c>
     </row>
     <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
           <t>Quechultenango</t>
@@ -3609,6 +4769,11 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -3622,6 +4787,11 @@
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
           <t>San Marcos</t>
@@ -3635,6 +4805,11 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>San Miguel Totolapan</t>
@@ -3648,9 +4823,14 @@
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Taxco de Alarcón</t>
+          <t>Taxco De Alarcón</t>
         </is>
       </c>
       <c r="C249">
@@ -3661,6 +4841,11 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>Tecoanapa</t>
@@ -3674,6 +4859,11 @@
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
           <t>Teloloapan</t>
@@ -3687,6 +4877,11 @@
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
           <t>Tetipac</t>
@@ -3700,9 +4895,14 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Tixtla de Guerrero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C253">
@@ -3713,6 +4913,11 @@
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>Tlacoachistlahuaca</t>
@@ -3726,6 +4931,11 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
           <t>Tlacoapa</t>
@@ -3739,9 +4949,14 @@
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C256">
@@ -3752,6 +4967,11 @@
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
           <t>Zirándaro</t>
@@ -3765,6 +4985,11 @@
       </c>
     </row>
     <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3796,6 +5021,11 @@
       </c>
     </row>
     <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
           <t>Actopan</t>
@@ -3809,6 +5039,11 @@
       </c>
     </row>
     <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
           <t>Apan</t>
@@ -3822,9 +5057,14 @@
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Atotonilco el Grande</t>
+          <t>Atotonilco El Grande</t>
         </is>
       </c>
       <c r="C262">
@@ -3835,6 +5075,11 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
           <t>Chapulhuacán</t>
@@ -3848,6 +5093,11 @@
       </c>
     </row>
     <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
           <t>Chilcuautla</t>
@@ -3861,6 +5111,11 @@
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
           <t>Epazoyucan</t>
@@ -3874,6 +5129,11 @@
       </c>
     </row>
     <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
           <t>Huautla</t>
@@ -3887,9 +5147,14 @@
       </c>
     </row>
     <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Huejutla de Reyes</t>
+          <t>Huejutla De Reyes</t>
         </is>
       </c>
       <c r="C267">
@@ -3900,6 +5165,11 @@
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
           <t>Huichapan</t>
@@ -3913,6 +5183,11 @@
       </c>
     </row>
     <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -3926,9 +5201,14 @@
       </c>
     </row>
     <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Jacala de Ledezma</t>
+          <t>Jacala De Ledezma</t>
         </is>
       </c>
       <c r="C270">
@@ -3939,6 +5219,11 @@
       </c>
     </row>
     <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
           <t>La Misión</t>
@@ -3952,6 +5237,11 @@
       </c>
     </row>
     <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B272" t="inlineStr">
         <is>
           <t>Metepec</t>
@@ -3965,6 +5255,11 @@
       </c>
     </row>
     <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
           <t>Metztitlán</t>
@@ -3978,9 +5273,14 @@
       </c>
     </row>
     <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Mixquiahuala de Juárez</t>
+          <t>Mixquiahuala De Juárez</t>
         </is>
       </c>
       <c r="C274">
@@ -3991,6 +5291,11 @@
       </c>
     </row>
     <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
           <t>Nicolás Flores</t>
@@ -4004,9 +5309,14 @@
       </c>
     </row>
     <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C276">
@@ -4017,6 +5327,11 @@
       </c>
     </row>
     <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
           <t>Pacula</t>
@@ -4030,6 +5345,11 @@
       </c>
     </row>
     <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B278" t="inlineStr">
         <is>
           <t>Pisaflores</t>
@@ -4043,6 +5363,11 @@
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>San Felipe Orizatlán</t>
@@ -4056,9 +5381,14 @@
       </c>
     </row>
     <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Santiago de Anaya</t>
+          <t>Santiago De Anaya</t>
         </is>
       </c>
       <c r="C280">
@@ -4069,6 +5399,11 @@
       </c>
     </row>
     <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
           <t>Singuilucan</t>
@@ -4082,6 +5417,11 @@
       </c>
     </row>
     <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B282" t="inlineStr">
         <is>
           <t>Tasquillo</t>
@@ -4095,6 +5435,11 @@
       </c>
     </row>
     <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
           <t>Tecozautla</t>
@@ -4108,9 +5453,14 @@
       </c>
     </row>
     <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Tenango de Doria</t>
+          <t>Tenango De Doria</t>
         </is>
       </c>
       <c r="C284">
@@ -4121,9 +5471,14 @@
       </c>
     </row>
     <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Tepehuacán de Guerrero</t>
+          <t>Tepehuacán De Guerrero</t>
         </is>
       </c>
       <c r="C285">
@@ -4134,9 +5489,14 @@
       </c>
     </row>
     <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Tepeji del Río de Ocampo</t>
+          <t>Tepeji Del Río De Ocampo</t>
         </is>
       </c>
       <c r="C286">
@@ -4147,9 +5507,14 @@
       </c>
     </row>
     <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Tezontepec de Aldama</t>
+          <t>Tezontepec De Aldama</t>
         </is>
       </c>
       <c r="C287">
@@ -4160,6 +5525,11 @@
       </c>
     </row>
     <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B288" t="inlineStr">
         <is>
           <t>Tizayuca</t>
@@ -4173,6 +5543,11 @@
       </c>
     </row>
     <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
           <t>Tlahuelilpan</t>
@@ -4186,6 +5561,11 @@
       </c>
     </row>
     <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
           <t>Tlahuiltepa</t>
@@ -4199,6 +5579,11 @@
       </c>
     </row>
     <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
           <t>Tlanchinol</t>
@@ -4212,6 +5597,11 @@
       </c>
     </row>
     <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B292" t="inlineStr">
         <is>
           <t>Tolcayuca</t>
@@ -4225,9 +5615,14 @@
       </c>
     </row>
     <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Tula de Allende</t>
+          <t>Tula De Allende</t>
         </is>
       </c>
       <c r="C293">
@@ -4238,9 +5633,14 @@
       </c>
     </row>
     <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C294">
@@ -4251,6 +5651,11 @@
       </c>
     </row>
     <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
           <t>Zimapán</t>
@@ -4264,6 +5669,11 @@
       </c>
     </row>
     <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4295,6 +5705,11 @@
       </c>
     </row>
     <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B298" t="inlineStr">
         <is>
           <t>Arandas</t>
@@ -4308,6 +5723,11 @@
       </c>
     </row>
     <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B299" t="inlineStr">
         <is>
           <t>Atenguillo</t>
@@ -4321,6 +5741,11 @@
       </c>
     </row>
     <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
           <t>Ayotlán</t>
@@ -4334,6 +5759,11 @@
       </c>
     </row>
     <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B301" t="inlineStr">
         <is>
           <t>Cuquío</t>
@@ -4347,6 +5777,11 @@
       </c>
     </row>
     <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
           <t>Degollado</t>
@@ -4360,9 +5795,14 @@
       </c>
     </row>
     <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Encarnación de Díaz</t>
+          <t>Encarnación De Díaz</t>
         </is>
       </c>
       <c r="C303">
@@ -4373,6 +5813,11 @@
       </c>
     </row>
     <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B304" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -4386,6 +5831,11 @@
       </c>
     </row>
     <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B305" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -4399,9 +5849,14 @@
       </c>
     </row>
     <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Jilotlán de los Dolores</t>
+          <t>Jilotlán De Los Dolores</t>
         </is>
       </c>
       <c r="C306">
@@ -4412,6 +5867,11 @@
       </c>
     </row>
     <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B307" t="inlineStr">
         <is>
           <t>La Barca</t>
@@ -4425,9 +5885,14 @@
       </c>
     </row>
     <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C308">
@@ -4438,6 +5903,11 @@
       </c>
     </row>
     <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr">
         <is>
           <t>Ocotlán</t>
@@ -4451,9 +5921,14 @@
       </c>
     </row>
     <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Ojuelos de Jalisco</t>
+          <t>Ojuelos De Jalisco</t>
         </is>
       </c>
       <c r="C310">
@@ -4464,6 +5939,11 @@
       </c>
     </row>
     <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B311" t="inlineStr">
         <is>
           <t>Puerto Vallarta</t>
@@ -4477,6 +5957,11 @@
       </c>
     </row>
     <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B312" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -4490,9 +5975,14 @@
       </c>
     </row>
     <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Talpa de Allende</t>
+          <t>Talpa De Allende</t>
         </is>
       </c>
       <c r="C313">
@@ -4503,6 +5993,11 @@
       </c>
     </row>
     <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B314" t="inlineStr">
         <is>
           <t>Teocaltiche</t>
@@ -4516,6 +6011,11 @@
       </c>
     </row>
     <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B315" t="inlineStr">
         <is>
           <t>Tequila</t>
@@ -4529,6 +6029,11 @@
       </c>
     </row>
     <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B316" t="inlineStr">
         <is>
           <t>Tlaquepaque</t>
@@ -4542,6 +6047,11 @@
       </c>
     </row>
     <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B317" t="inlineStr">
         <is>
           <t>Tomatlán</t>
@@ -4555,6 +6065,11 @@
       </c>
     </row>
     <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B318" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -4568,6 +6083,11 @@
       </c>
     </row>
     <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B319" t="inlineStr">
         <is>
           <t>Tototlán</t>
@@ -4581,6 +6101,11 @@
       </c>
     </row>
     <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B320" t="inlineStr">
         <is>
           <t>Villa Purificación</t>
@@ -4594,6 +6119,11 @@
       </c>
     </row>
     <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B321" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -4607,6 +6137,11 @@
       </c>
     </row>
     <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B322" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4638,6 +6173,11 @@
       </c>
     </row>
     <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B324" t="inlineStr">
         <is>
           <t>Angangueo</t>
@@ -4651,6 +6191,11 @@
       </c>
     </row>
     <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B325" t="inlineStr">
         <is>
           <t>Apatzingán</t>
@@ -4664,6 +6209,11 @@
       </c>
     </row>
     <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B326" t="inlineStr">
         <is>
           <t>Buenavista</t>
@@ -4677,6 +6227,11 @@
       </c>
     </row>
     <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B327" t="inlineStr">
         <is>
           <t>Carácuaro</t>
@@ -4690,6 +6245,11 @@
       </c>
     </row>
     <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B328" t="inlineStr">
         <is>
           <t>Churumuco</t>
@@ -4703,6 +6263,11 @@
       </c>
     </row>
     <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B329" t="inlineStr">
         <is>
           <t>Contepec</t>
@@ -4716,6 +6281,11 @@
       </c>
     </row>
     <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B330" t="inlineStr">
         <is>
           <t>Cotija</t>
@@ -4729,6 +6299,11 @@
       </c>
     </row>
     <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B331" t="inlineStr">
         <is>
           <t>Epitacio Huerta</t>
@@ -4742,6 +6317,11 @@
       </c>
     </row>
     <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B332" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -4755,6 +6335,11 @@
       </c>
     </row>
     <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B333" t="inlineStr">
         <is>
           <t>Huetamo</t>
@@ -4768,6 +6353,11 @@
       </c>
     </row>
     <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B334" t="inlineStr">
         <is>
           <t>Irimbo</t>
@@ -4781,6 +6371,11 @@
       </c>
     </row>
     <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B335" t="inlineStr">
         <is>
           <t>Jiquilpan</t>
@@ -4794,6 +6389,11 @@
       </c>
     </row>
     <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B336" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -4807,6 +6407,11 @@
       </c>
     </row>
     <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B337" t="inlineStr">
         <is>
           <t>La Huacana</t>
@@ -4820,6 +6425,11 @@
       </c>
     </row>
     <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B338" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -4833,6 +6443,11 @@
       </c>
     </row>
     <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B339" t="inlineStr">
         <is>
           <t>Lagunillas</t>
@@ -4846,6 +6461,11 @@
       </c>
     </row>
     <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B340" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -4859,6 +6479,11 @@
       </c>
     </row>
     <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B341" t="inlineStr">
         <is>
           <t>Los Reyes</t>
@@ -4872,6 +6497,11 @@
       </c>
     </row>
     <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B342" t="inlineStr">
         <is>
           <t>Maravatío</t>
@@ -4885,6 +6515,11 @@
       </c>
     </row>
     <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B343" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -4898,6 +6533,11 @@
       </c>
     </row>
     <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B344" t="inlineStr">
         <is>
           <t>Múgica</t>
@@ -4911,6 +6551,11 @@
       </c>
     </row>
     <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B345" t="inlineStr">
         <is>
           <t>Nahuatzen</t>
@@ -4924,6 +6569,11 @@
       </c>
     </row>
     <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B346" t="inlineStr">
         <is>
           <t>Paracho</t>
@@ -4937,6 +6587,11 @@
       </c>
     </row>
     <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B347" t="inlineStr">
         <is>
           <t>Parácuaro</t>
@@ -4950,6 +6605,11 @@
       </c>
     </row>
     <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B348" t="inlineStr">
         <is>
           <t>Puruándiro</t>
@@ -4963,6 +6623,11 @@
       </c>
     </row>
     <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B349" t="inlineStr">
         <is>
           <t>Quiroga</t>
@@ -4976,6 +6641,11 @@
       </c>
     </row>
     <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B350" t="inlineStr">
         <is>
           <t>San Lucas</t>
@@ -4989,6 +6659,11 @@
       </c>
     </row>
     <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B351" t="inlineStr">
         <is>
           <t>Santa Ana Maya</t>
@@ -5002,6 +6677,11 @@
       </c>
     </row>
     <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B352" t="inlineStr">
         <is>
           <t>Tacámbaro</t>
@@ -5015,6 +6695,11 @@
       </c>
     </row>
     <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B353" t="inlineStr">
         <is>
           <t>Tepalcatepec</t>
@@ -5028,9 +6713,14 @@
       </c>
     </row>
     <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Tiquicheo de Nicolás Romero</t>
+          <t>Tiquicheo De Nicolás Romero</t>
         </is>
       </c>
       <c r="C354">
@@ -5041,6 +6731,11 @@
       </c>
     </row>
     <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B355" t="inlineStr">
         <is>
           <t>Tumbiscatío</t>
@@ -5054,6 +6749,11 @@
       </c>
     </row>
     <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B356" t="inlineStr">
         <is>
           <t>Turicato</t>
@@ -5067,6 +6767,11 @@
       </c>
     </row>
     <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B357" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -5080,6 +6785,11 @@
       </c>
     </row>
     <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B358" t="inlineStr">
         <is>
           <t>Tuzantla</t>
@@ -5093,6 +6803,11 @@
       </c>
     </row>
     <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B359" t="inlineStr">
         <is>
           <t>Tzintzuntzan</t>
@@ -5106,6 +6821,11 @@
       </c>
     </row>
     <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B360" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -5119,6 +6839,11 @@
       </c>
     </row>
     <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B361" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -5132,6 +6857,11 @@
       </c>
     </row>
     <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B362" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -5145,6 +6875,11 @@
       </c>
     </row>
     <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B363" t="inlineStr">
         <is>
           <t>Zinapécuaro</t>
@@ -5158,6 +6893,11 @@
       </c>
     </row>
     <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B364" t="inlineStr">
         <is>
           <t>Ziracuaretiro</t>
@@ -5171,6 +6911,11 @@
       </c>
     </row>
     <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B365" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -5184,6 +6929,11 @@
       </c>
     </row>
     <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B366" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5215,6 +6965,11 @@
       </c>
     </row>
     <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B368" t="inlineStr">
         <is>
           <t>Cuautla</t>
@@ -5228,6 +6983,11 @@
       </c>
     </row>
     <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B369" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -5241,9 +7001,14 @@
       </c>
     </row>
     <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Puente de Ixtla</t>
+          <t>Puente De Ixtla</t>
         </is>
       </c>
       <c r="C370">
@@ -5254,6 +7019,11 @@
       </c>
     </row>
     <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B371" t="inlineStr">
         <is>
           <t>Temixco</t>
@@ -5267,6 +7037,11 @@
       </c>
     </row>
     <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B372" t="inlineStr">
         <is>
           <t>Temoac</t>
@@ -5280,9 +7055,14 @@
       </c>
     </row>
     <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Tlaltizapán de Zapata</t>
+          <t>Tlaltizapán De Zapata</t>
         </is>
       </c>
       <c r="C373">
@@ -5293,6 +7073,11 @@
       </c>
     </row>
     <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B374" t="inlineStr">
         <is>
           <t>Yautepec</t>
@@ -5306,9 +7091,14 @@
       </c>
     </row>
     <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Zacualpan de Amilpas</t>
+          <t>Zacualpan De Amilpas</t>
         </is>
       </c>
       <c r="C375">
@@ -5319,6 +7109,11 @@
       </c>
     </row>
     <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B376" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5350,9 +7145,14 @@
       </c>
     </row>
     <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Santa María del Oro</t>
+          <t>Santa María Del Oro</t>
         </is>
       </c>
       <c r="C378">
@@ -5363,6 +7163,11 @@
       </c>
     </row>
     <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B379" t="inlineStr">
         <is>
           <t>Santiago Ixcuintla</t>
@@ -5376,6 +7181,11 @@
       </c>
     </row>
     <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B380" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -5389,6 +7199,11 @@
       </c>
     </row>
     <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B381" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -5402,6 +7217,11 @@
       </c>
     </row>
     <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B382" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5433,6 +7253,11 @@
       </c>
     </row>
     <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B384" t="inlineStr">
         <is>
           <t>Doctor Arroyo</t>
@@ -5446,6 +7271,11 @@
       </c>
     </row>
     <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B385" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -5459,6 +7289,11 @@
       </c>
     </row>
     <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B386" t="inlineStr">
         <is>
           <t>Hualahuises</t>
@@ -5472,6 +7307,11 @@
       </c>
     </row>
     <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B387" t="inlineStr">
         <is>
           <t>Linares</t>
@@ -5485,9 +7325,14 @@
       </c>
     </row>
     <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Mier y Noriega</t>
+          <t>Mier Y Noriega</t>
         </is>
       </c>
       <c r="C388">
@@ -5498,9 +7343,14 @@
       </c>
     </row>
     <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>MonteMorelos</t>
+          <t>Montemorelos</t>
         </is>
       </c>
       <c r="C389">
@@ -5511,6 +7361,11 @@
       </c>
     </row>
     <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B390" t="inlineStr">
         <is>
           <t>Monterrey</t>
@@ -5524,6 +7379,11 @@
       </c>
     </row>
     <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B391" t="inlineStr">
         <is>
           <t>Sabinas Hidalgo</t>
@@ -5537,9 +7397,14 @@
       </c>
     </row>
     <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>San Nicolás de los Garza</t>
+          <t>San Nicolás De Los Garza</t>
         </is>
       </c>
       <c r="C392">
@@ -5550,6 +7415,11 @@
       </c>
     </row>
     <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B393" t="inlineStr">
         <is>
           <t>San Pedro Garza García</t>
@@ -5563,6 +7433,11 @@
       </c>
     </row>
     <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B394" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5594,6 +7469,11 @@
       </c>
     </row>
     <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B396" t="inlineStr">
         <is>
           <t>Cosolapa</t>
@@ -5607,9 +7487,14 @@
       </c>
     </row>
     <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Ejutla de Crespo</t>
+          <t>Heroica Ciudad De Ejutla De Crespo</t>
         </is>
       </c>
       <c r="C397">
@@ -5620,9 +7505,14 @@
       </c>
     </row>
     <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Juchitán de Zaragoza</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C398">
@@ -5633,6 +7523,11 @@
       </c>
     </row>
     <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B399" t="inlineStr">
         <is>
           <t>Matías Romero Avendaño</t>
@@ -5646,9 +7541,14 @@
       </c>
     </row>
     <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Miahuatlán de Porfirio Díaz</t>
+          <t>Miahuatlán De Porfirio Díaz</t>
         </is>
       </c>
       <c r="C400">
@@ -5659,9 +7559,14 @@
       </c>
     </row>
     <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C401">
@@ -5672,9 +7577,14 @@
       </c>
     </row>
     <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Ocotlán de Morelos</t>
+          <t>Ocotlán De Morelos</t>
         </is>
       </c>
       <c r="C402">
@@ -5685,9 +7595,14 @@
       </c>
     </row>
     <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Putla Villa de Guerrero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C403">
@@ -5698,6 +7613,11 @@
       </c>
     </row>
     <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B404" t="inlineStr">
         <is>
           <t>Salina Cruz</t>
@@ -5711,6 +7631,11 @@
       </c>
     </row>
     <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B405" t="inlineStr">
         <is>
           <t>San Agustín Loxicha</t>
@@ -5724,6 +7649,11 @@
       </c>
     </row>
     <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B406" t="inlineStr">
         <is>
           <t>San Andrés Huayápam</t>
@@ -5737,6 +7667,11 @@
       </c>
     </row>
     <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B407" t="inlineStr">
         <is>
           <t>San Antonio Tepetlapa</t>
@@ -5750,6 +7685,11 @@
       </c>
     </row>
     <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B408" t="inlineStr">
         <is>
           <t>San Blas Atempa</t>
@@ -5763,6 +7703,11 @@
       </c>
     </row>
     <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B409" t="inlineStr">
         <is>
           <t>San Felipe Usila</t>
@@ -5776,6 +7721,11 @@
       </c>
     </row>
     <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B410" t="inlineStr">
         <is>
           <t>San Francisco Chapulapa</t>
@@ -5789,6 +7739,11 @@
       </c>
     </row>
     <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B411" t="inlineStr">
         <is>
           <t>San Francisco Ixhuatán</t>
@@ -5802,6 +7757,11 @@
       </c>
     </row>
     <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B412" t="inlineStr">
         <is>
           <t>San Jerónimo Taviche</t>
@@ -5815,6 +7775,11 @@
       </c>
     </row>
     <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B413" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -5828,6 +7793,11 @@
       </c>
     </row>
     <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B414" t="inlineStr">
         <is>
           <t>San Juan Bautista Valle Nacional</t>
@@ -5841,6 +7811,11 @@
       </c>
     </row>
     <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B415" t="inlineStr">
         <is>
           <t>San Juan Cacahuatepec</t>
@@ -5854,6 +7829,11 @@
       </c>
     </row>
     <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B416" t="inlineStr">
         <is>
           <t>San Juan Cieneguilla</t>
@@ -5867,6 +7847,11 @@
       </c>
     </row>
     <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B417" t="inlineStr">
         <is>
           <t>San Juan Cotzocón</t>
@@ -5880,6 +7865,11 @@
       </c>
     </row>
     <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B418" t="inlineStr">
         <is>
           <t>San Juan Guichicovi</t>
@@ -5893,6 +7883,11 @@
       </c>
     </row>
     <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B419" t="inlineStr">
         <is>
           <t>San Juan Lachigalla</t>
@@ -5906,6 +7901,11 @@
       </c>
     </row>
     <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B420" t="inlineStr">
         <is>
           <t>San Juan Quiahije</t>
@@ -5919,6 +7919,11 @@
       </c>
     </row>
     <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B421" t="inlineStr">
         <is>
           <t>San Lucas Ojitlán</t>
@@ -5932,6 +7937,11 @@
       </c>
     </row>
     <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B422" t="inlineStr">
         <is>
           <t>San Luis Amatlán</t>
@@ -5945,6 +7955,11 @@
       </c>
     </row>
     <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B423" t="inlineStr">
         <is>
           <t>San Martín Peras</t>
@@ -5958,9 +7973,14 @@
       </c>
     </row>
     <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>San Miguel el Grande</t>
+          <t>San Miguel El Grande</t>
         </is>
       </c>
       <c r="C424">
@@ -5971,6 +7991,11 @@
       </c>
     </row>
     <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B425" t="inlineStr">
         <is>
           <t>San Miguel Panixtlahuaca</t>
@@ -5984,6 +8009,11 @@
       </c>
     </row>
     <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B426" t="inlineStr">
         <is>
           <t>San Miguel Peras</t>
@@ -5997,6 +8027,11 @@
       </c>
     </row>
     <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B427" t="inlineStr">
         <is>
           <t>San Miguel Soyaltepec</t>
@@ -6010,6 +8045,11 @@
       </c>
     </row>
     <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B428" t="inlineStr">
         <is>
           <t>San Pedro Huilotepec</t>
@@ -6023,6 +8063,11 @@
       </c>
     </row>
     <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B429" t="inlineStr">
         <is>
           <t>San Pedro Jicayán</t>
@@ -6036,6 +8081,11 @@
       </c>
     </row>
     <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B430" t="inlineStr">
         <is>
           <t>San Pedro Mixtepec - Distr. 22 -</t>
@@ -6049,6 +8099,11 @@
       </c>
     </row>
     <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B431" t="inlineStr">
         <is>
           <t>San Pedro Pochutla</t>
@@ -6062,6 +8117,11 @@
       </c>
     </row>
     <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B432" t="inlineStr">
         <is>
           <t>San Vicente Lachixío</t>
@@ -6075,6 +8135,11 @@
       </c>
     </row>
     <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B433" t="inlineStr">
         <is>
           <t>Santa Catarina Juquila</t>
@@ -6088,6 +8153,11 @@
       </c>
     </row>
     <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B434" t="inlineStr">
         <is>
           <t>Santa Cruz Zenzontepec</t>
@@ -6101,6 +8171,11 @@
       </c>
     </row>
     <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B435" t="inlineStr">
         <is>
           <t>Santa María Alotepec</t>
@@ -6114,6 +8189,11 @@
       </c>
     </row>
     <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B436" t="inlineStr">
         <is>
           <t>Santa María Pápalo</t>
@@ -6127,6 +8207,11 @@
       </c>
     </row>
     <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B437" t="inlineStr">
         <is>
           <t>Santa María Temaxcaltepec</t>
@@ -6140,6 +8225,11 @@
       </c>
     </row>
     <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B438" t="inlineStr">
         <is>
           <t>Santa María Tlahuitoltepec</t>
@@ -6153,6 +8243,11 @@
       </c>
     </row>
     <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B439" t="inlineStr">
         <is>
           <t>Santa María Tonameca</t>
@@ -6166,6 +8261,11 @@
       </c>
     </row>
     <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B440" t="inlineStr">
         <is>
           <t>Santa María Totolapilla</t>
@@ -6179,6 +8279,11 @@
       </c>
     </row>
     <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B441" t="inlineStr">
         <is>
           <t>Santiago Astata</t>
@@ -6192,6 +8297,11 @@
       </c>
     </row>
     <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B442" t="inlineStr">
         <is>
           <t>Santiago Comaltepec</t>
@@ -6205,6 +8315,11 @@
       </c>
     </row>
     <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B443" t="inlineStr">
         <is>
           <t>Santiago Jamiltepec</t>
@@ -6218,6 +8333,11 @@
       </c>
     </row>
     <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B444" t="inlineStr">
         <is>
           <t>Santiago Nacaltepec</t>
@@ -6231,6 +8351,11 @@
       </c>
     </row>
     <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B445" t="inlineStr">
         <is>
           <t>Santiago Yaitepec</t>
@@ -6244,6 +8369,11 @@
       </c>
     </row>
     <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B446" t="inlineStr">
         <is>
           <t>Santiago Yosondúa</t>
@@ -6257,9 +8387,14 @@
       </c>
     </row>
     <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Santo Domingo de Morelos</t>
+          <t>Santo Domingo De Morelos</t>
         </is>
       </c>
       <c r="C447">
@@ -6270,6 +8405,11 @@
       </c>
     </row>
     <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B448" t="inlineStr">
         <is>
           <t>Santo Domingo Nuxaá</t>
@@ -6283,6 +8423,11 @@
       </c>
     </row>
     <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B449" t="inlineStr">
         <is>
           <t>Santo Domingo Tehuantepec</t>
@@ -6296,6 +8441,11 @@
       </c>
     </row>
     <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B450" t="inlineStr">
         <is>
           <t>Silacayoápam</t>
@@ -6309,9 +8459,14 @@
       </c>
     </row>
     <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Teotitlán de Flores Magón</t>
+          <t>Teotitlán De Flores Magón</t>
         </is>
       </c>
       <c r="C451">
@@ -6322,9 +8477,14 @@
       </c>
     </row>
     <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Tlacolula de Matamoros</t>
+          <t>Tlacolula De Matamoros</t>
         </is>
       </c>
       <c r="C452">
@@ -6335,9 +8495,14 @@
       </c>
     </row>
     <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Villa de Tututepec de Melchor Ocampo</t>
+          <t>Villa De Tututepec De Melchor Ocampo</t>
         </is>
       </c>
       <c r="C453">
@@ -6348,6 +8513,11 @@
       </c>
     </row>
     <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B454" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6379,6 +8549,11 @@
       </c>
     </row>
     <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B456" t="inlineStr">
         <is>
           <t>Aquixtla</t>
@@ -6392,6 +8567,11 @@
       </c>
     </row>
     <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B457" t="inlineStr">
         <is>
           <t>Atempan</t>
@@ -6405,6 +8585,11 @@
       </c>
     </row>
     <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B458" t="inlineStr">
         <is>
           <t>Atlixco</t>
@@ -6418,9 +8603,14 @@
       </c>
     </row>
     <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Ayotoxco de Guerrero</t>
+          <t>Ayotoxco De Guerrero</t>
         </is>
       </c>
       <c r="C459">
@@ -6431,6 +8621,11 @@
       </c>
     </row>
     <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B460" t="inlineStr">
         <is>
           <t>Chichiquila</t>
@@ -6444,6 +8639,11 @@
       </c>
     </row>
     <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B461" t="inlineStr">
         <is>
           <t>Chietla</t>
@@ -6457,6 +8657,11 @@
       </c>
     </row>
     <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B462" t="inlineStr">
         <is>
           <t>Chignahuapan</t>
@@ -6470,6 +8675,11 @@
       </c>
     </row>
     <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B463" t="inlineStr">
         <is>
           <t>Cohetzala</t>
@@ -6483,6 +8693,11 @@
       </c>
     </row>
     <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B464" t="inlineStr">
         <is>
           <t>Cuautlancingo</t>
@@ -6496,9 +8711,14 @@
       </c>
     </row>
     <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Cuetzalan del Progreso</t>
+          <t>Cuetzalan Del Progreso</t>
         </is>
       </c>
       <c r="C465">
@@ -6509,6 +8729,11 @@
       </c>
     </row>
     <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B466" t="inlineStr">
         <is>
           <t>Eloxochitlán</t>
@@ -6522,6 +8747,11 @@
       </c>
     </row>
     <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B467" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -6535,6 +8765,11 @@
       </c>
     </row>
     <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B468" t="inlineStr">
         <is>
           <t>Huauchinango</t>
@@ -6548,6 +8783,11 @@
       </c>
     </row>
     <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B469" t="inlineStr">
         <is>
           <t>Huejotzingo</t>
@@ -6561,6 +8801,11 @@
       </c>
     </row>
     <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B470" t="inlineStr">
         <is>
           <t>Hueyapan</t>
@@ -6574,6 +8819,11 @@
       </c>
     </row>
     <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B471" t="inlineStr">
         <is>
           <t>Hueytlalpan</t>
@@ -6587,6 +8837,11 @@
       </c>
     </row>
     <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B472" t="inlineStr">
         <is>
           <t>Ixtacamaxtitlán</t>
@@ -6600,9 +8855,14 @@
       </c>
     </row>
     <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C473">
@@ -6613,6 +8873,11 @@
       </c>
     </row>
     <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B474" t="inlineStr">
         <is>
           <t>Jalpan</t>
@@ -6626,6 +8891,11 @@
       </c>
     </row>
     <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B475" t="inlineStr">
         <is>
           <t>Jolalpan</t>
@@ -6639,6 +8909,11 @@
       </c>
     </row>
     <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B476" t="inlineStr">
         <is>
           <t>Juan C. Bonilla</t>
@@ -6652,9 +8927,14 @@
       </c>
     </row>
     <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Los Reyes de Juárez</t>
+          <t>Los Reyes De Juárez</t>
         </is>
       </c>
       <c r="C477">
@@ -6665,6 +8945,11 @@
       </c>
     </row>
     <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B478" t="inlineStr">
         <is>
           <t>Pahuatlán</t>
@@ -6678,9 +8963,14 @@
       </c>
     </row>
     <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Palmar de Bravo</t>
+          <t>Palmar De Bravo</t>
         </is>
       </c>
       <c r="C479">
@@ -6691,6 +8981,11 @@
       </c>
     </row>
     <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B480" t="inlineStr">
         <is>
           <t>Pantepec</t>
@@ -6704,6 +8999,11 @@
       </c>
     </row>
     <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B481" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -6717,6 +9017,11 @@
       </c>
     </row>
     <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B482" t="inlineStr">
         <is>
           <t>Quecholac</t>
@@ -6730,9 +9035,14 @@
       </c>
     </row>
     <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>San Salvador el Seco</t>
+          <t>San Salvador El Seco</t>
         </is>
       </c>
       <c r="C483">
@@ -6743,6 +9053,11 @@
       </c>
     </row>
     <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B484" t="inlineStr">
         <is>
           <t>Santiago Miahuatlán</t>
@@ -6756,6 +9071,11 @@
       </c>
     </row>
     <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B485" t="inlineStr">
         <is>
           <t>Tecamachalco</t>
@@ -6769,6 +9089,11 @@
       </c>
     </row>
     <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B486" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -6782,6 +9107,11 @@
       </c>
     </row>
     <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B487" t="inlineStr">
         <is>
           <t>Tehuitzingo</t>
@@ -6795,6 +9125,11 @@
       </c>
     </row>
     <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B488" t="inlineStr">
         <is>
           <t>Tenampulco</t>
@@ -6808,6 +9143,11 @@
       </c>
     </row>
     <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B489" t="inlineStr">
         <is>
           <t>Tepeojuma</t>
@@ -6821,9 +9161,14 @@
       </c>
     </row>
     <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Tepexi de Rodríguez</t>
+          <t>Tepexi De Rodríguez</t>
         </is>
       </c>
       <c r="C490">
@@ -6834,9 +9179,14 @@
       </c>
     </row>
     <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Teteles de Avila Castillo</t>
+          <t>Teteles De Avila Castillo</t>
         </is>
       </c>
       <c r="C491">
@@ -6847,6 +9197,11 @@
       </c>
     </row>
     <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B492" t="inlineStr">
         <is>
           <t>Teziutlán</t>
@@ -6860,6 +9215,11 @@
       </c>
     </row>
     <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B493" t="inlineStr">
         <is>
           <t>Tlachichuca</t>
@@ -6873,9 +9233,14 @@
       </c>
     </row>
     <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Tlacotepec de Benito Juárez</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C494">
@@ -6886,6 +9251,11 @@
       </c>
     </row>
     <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B495" t="inlineStr">
         <is>
           <t>Tlahuapan</t>
@@ -6899,6 +9269,11 @@
       </c>
     </row>
     <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B496" t="inlineStr">
         <is>
           <t>Tlaola</t>
@@ -6912,6 +9287,11 @@
       </c>
     </row>
     <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B497" t="inlineStr">
         <is>
           <t>Tlatlauquitepec</t>
@@ -6925,6 +9305,11 @@
       </c>
     </row>
     <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B498" t="inlineStr">
         <is>
           <t>Tulcingo</t>
@@ -6938,9 +9323,14 @@
       </c>
     </row>
     <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Tuzamapan de Galeana</t>
+          <t>Tuzamapan De Galeana</t>
         </is>
       </c>
       <c r="C499">
@@ -6951,6 +9341,11 @@
       </c>
     </row>
     <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B500" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -6964,6 +9359,11 @@
       </c>
     </row>
     <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B501" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -6977,6 +9377,11 @@
       </c>
     </row>
     <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B502" t="inlineStr">
         <is>
           <t>Xicotepec</t>
@@ -6990,6 +9395,11 @@
       </c>
     </row>
     <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B503" t="inlineStr">
         <is>
           <t>Zacapoaxtla</t>
@@ -7003,6 +9413,11 @@
       </c>
     </row>
     <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B504" t="inlineStr">
         <is>
           <t>Zacatlán</t>
@@ -7016,6 +9431,11 @@
       </c>
     </row>
     <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B505" t="inlineStr">
         <is>
           <t>Zihuateutla</t>
@@ -7029,6 +9449,11 @@
       </c>
     </row>
     <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B506" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7049,7 +9474,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Amealco de Bonfil</t>
+          <t>Amealco De Bonfil</t>
         </is>
       </c>
       <c r="C507">
@@ -7060,6 +9485,11 @@
       </c>
     </row>
     <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B508" t="inlineStr">
         <is>
           <t>Arroyo Seco</t>
@@ -7073,9 +9503,14 @@
       </c>
     </row>
     <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C509">
@@ -7086,6 +9521,11 @@
       </c>
     </row>
     <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B510" t="inlineStr">
         <is>
           <t>Corregidora</t>
@@ -7099,6 +9539,11 @@
       </c>
     </row>
     <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B511" t="inlineStr">
         <is>
           <t>Huimilpan</t>
@@ -7112,9 +9557,14 @@
       </c>
     </row>
     <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Jalpan de Serra</t>
+          <t>Jalpan De Serra</t>
         </is>
       </c>
       <c r="C512">
@@ -7125,9 +9575,14 @@
       </c>
     </row>
     <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Landa de Matamoros</t>
+          <t>Landa De Matamoros</t>
         </is>
       </c>
       <c r="C513">
@@ -7138,6 +9593,11 @@
       </c>
     </row>
     <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B514" t="inlineStr">
         <is>
           <t>Pedro Escobedo</t>
@@ -7151,9 +9611,14 @@
       </c>
     </row>
     <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Pinal de Amoles</t>
+          <t>Pinal De Amoles</t>
         </is>
       </c>
       <c r="C515">
@@ -7164,6 +9629,11 @@
       </c>
     </row>
     <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B516" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -7177,9 +9647,14 @@
       </c>
     </row>
     <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C517">
@@ -7190,6 +9665,11 @@
       </c>
     </row>
     <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B518" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7221,6 +9701,11 @@
       </c>
     </row>
     <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B520" t="inlineStr">
         <is>
           <t>Othón P. Blanco</t>
@@ -7234,6 +9719,11 @@
       </c>
     </row>
     <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B521" t="inlineStr">
         <is>
           <t>Solidaridad</t>
@@ -7247,6 +9737,11 @@
       </c>
     </row>
     <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B522" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7278,6 +9773,11 @@
       </c>
     </row>
     <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B524" t="inlineStr">
         <is>
           <t>Aquismón</t>
@@ -7291,6 +9791,11 @@
       </c>
     </row>
     <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B525" t="inlineStr">
         <is>
           <t>Cárdenas</t>
@@ -7304,6 +9809,11 @@
       </c>
     </row>
     <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B526" t="inlineStr">
         <is>
           <t>Catorce</t>
@@ -7317,6 +9827,11 @@
       </c>
     </row>
     <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B527" t="inlineStr">
         <is>
           <t>Cerritos</t>
@@ -7330,6 +9845,11 @@
       </c>
     </row>
     <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B528" t="inlineStr">
         <is>
           <t>Charcas</t>
@@ -7343,9 +9863,14 @@
       </c>
     </row>
     <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Ciudad del Maíz</t>
+          <t>Ciudad Del Maíz</t>
         </is>
       </c>
       <c r="C529">
@@ -7356,6 +9881,11 @@
       </c>
     </row>
     <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B530" t="inlineStr">
         <is>
           <t>Ciudad Fernández</t>
@@ -7369,6 +9899,11 @@
       </c>
     </row>
     <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B531" t="inlineStr">
         <is>
           <t>Ciudad Valles</t>
@@ -7382,6 +9917,11 @@
       </c>
     </row>
     <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B532" t="inlineStr">
         <is>
           <t>Ebano</t>
@@ -7395,6 +9935,11 @@
       </c>
     </row>
     <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B533" t="inlineStr">
         <is>
           <t>El Naranjo</t>
@@ -7408,6 +9953,11 @@
       </c>
     </row>
     <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B534" t="inlineStr">
         <is>
           <t>Guadalcázar</t>
@@ -7421,6 +9971,11 @@
       </c>
     </row>
     <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B535" t="inlineStr">
         <is>
           <t>Huehuetlán</t>
@@ -7434,6 +9989,11 @@
       </c>
     </row>
     <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B536" t="inlineStr">
         <is>
           <t>Lagunillas</t>
@@ -7447,6 +10007,11 @@
       </c>
     </row>
     <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B537" t="inlineStr">
         <is>
           <t>Matehuala</t>
@@ -7460,9 +10025,14 @@
       </c>
     </row>
     <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Mexquitic de Carmona</t>
+          <t>Mexquitic De Carmona</t>
         </is>
       </c>
       <c r="C538">
@@ -7473,6 +10043,11 @@
       </c>
     </row>
     <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B539" t="inlineStr">
         <is>
           <t>Moctezuma</t>
@@ -7486,6 +10061,11 @@
       </c>
     </row>
     <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B540" t="inlineStr">
         <is>
           <t>Rayón</t>
@@ -7499,6 +10079,11 @@
       </c>
     </row>
     <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B541" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -7512,6 +10097,11 @@
       </c>
     </row>
     <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B542" t="inlineStr">
         <is>
           <t>Salinas</t>
@@ -7525,9 +10115,14 @@
       </c>
     </row>
     <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>San Ciro de Acosta</t>
+          <t>San Ciro De Acosta</t>
         </is>
       </c>
       <c r="C543">
@@ -7538,6 +10133,11 @@
       </c>
     </row>
     <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B544" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -7551,6 +10151,11 @@
       </c>
     </row>
     <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B545" t="inlineStr">
         <is>
           <t>San Martín Chalchicuautla</t>
@@ -7564,6 +10169,11 @@
       </c>
     </row>
     <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B546" t="inlineStr">
         <is>
           <t>San Nicolás Tolentino</t>
@@ -7577,6 +10187,11 @@
       </c>
     </row>
     <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B547" t="inlineStr">
         <is>
           <t>Santa Catarina</t>
@@ -7590,6 +10205,11 @@
       </c>
     </row>
     <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B548" t="inlineStr">
         <is>
           <t>Tamasopo</t>
@@ -7603,6 +10223,11 @@
       </c>
     </row>
     <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B549" t="inlineStr">
         <is>
           <t>Tamazunchale</t>
@@ -7616,6 +10241,11 @@
       </c>
     </row>
     <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B550" t="inlineStr">
         <is>
           <t>Tamuín</t>
@@ -7629,6 +10259,11 @@
       </c>
     </row>
     <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B551" t="inlineStr">
         <is>
           <t>Tanlajás</t>
@@ -7642,9 +10277,14 @@
       </c>
     </row>
     <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Tanquián de Escobedo</t>
+          <t>Tanquián De Escobedo</t>
         </is>
       </c>
       <c r="C552">
@@ -7655,6 +10295,11 @@
       </c>
     </row>
     <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B553" t="inlineStr">
         <is>
           <t>Tierra Nueva</t>
@@ -7668,6 +10313,11 @@
       </c>
     </row>
     <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B554" t="inlineStr">
         <is>
           <t>Vanegas</t>
@@ -7681,6 +10331,11 @@
       </c>
     </row>
     <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B555" t="inlineStr">
         <is>
           <t>Venado</t>
@@ -7694,9 +10349,14 @@
       </c>
     </row>
     <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Villa de Arista</t>
+          <t>Villa De Arista</t>
         </is>
       </c>
       <c r="C556">
@@ -7707,9 +10367,14 @@
       </c>
     </row>
     <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Villa de Arriaga</t>
+          <t>Villa De Arriaga</t>
         </is>
       </c>
       <c r="C557">
@@ -7720,9 +10385,14 @@
       </c>
     </row>
     <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Villa de Guadalupe</t>
+          <t>Villa De Guadalupe</t>
         </is>
       </c>
       <c r="C558">
@@ -7733,9 +10403,14 @@
       </c>
     </row>
     <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Villa de Ramos</t>
+          <t>Villa De Ramos</t>
         </is>
       </c>
       <c r="C559">
@@ -7746,9 +10421,14 @@
       </c>
     </row>
     <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Villa de Reyes</t>
+          <t>Villa De Reyes</t>
         </is>
       </c>
       <c r="C560">
@@ -7759,6 +10439,11 @@
       </c>
     </row>
     <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B561" t="inlineStr">
         <is>
           <t>Villa Hidalgo</t>
@@ -7772,6 +10457,11 @@
       </c>
     </row>
     <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B562" t="inlineStr">
         <is>
           <t>Villa Juárez</t>
@@ -7785,6 +10475,11 @@
       </c>
     </row>
     <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B563" t="inlineStr">
         <is>
           <t>Xilitla</t>
@@ -7798,6 +10493,11 @@
       </c>
     </row>
     <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B564" t="inlineStr">
         <is>
           <t>Zaragoza</t>
@@ -7811,6 +10511,11 @@
       </c>
     </row>
     <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B565" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7842,6 +10547,11 @@
       </c>
     </row>
     <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B567" t="inlineStr">
         <is>
           <t>Culiacán</t>
@@ -7855,6 +10565,11 @@
       </c>
     </row>
     <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B568" t="inlineStr">
         <is>
           <t>El Fuerte</t>
@@ -7868,6 +10583,11 @@
       </c>
     </row>
     <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B569" t="inlineStr">
         <is>
           <t>Guasave</t>
@@ -7881,6 +10601,11 @@
       </c>
     </row>
     <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B570" t="inlineStr">
         <is>
           <t>Mazatlán</t>
@@ -7894,6 +10619,11 @@
       </c>
     </row>
     <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B571" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7903,7 +10633,7 @@
         <v>25</v>
       </c>
       <c r="D571">
-        <v>0.009686168151879117</v>
+        <v>0.009686168151879115</v>
       </c>
     </row>
     <row r="572">
@@ -7925,6 +10655,11 @@
       </c>
     </row>
     <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B573" t="inlineStr">
         <is>
           <t>Cajeme</t>
@@ -7938,6 +10673,11 @@
       </c>
     </row>
     <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B574" t="inlineStr">
         <is>
           <t>Guaymas</t>
@@ -7951,6 +10691,11 @@
       </c>
     </row>
     <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B575" t="inlineStr">
         <is>
           <t>Hermosillo</t>
@@ -7964,6 +10709,11 @@
       </c>
     </row>
     <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B576" t="inlineStr">
         <is>
           <t>Huatabampo</t>
@@ -7977,6 +10727,11 @@
       </c>
     </row>
     <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B577" t="inlineStr">
         <is>
           <t>Navojoa</t>
@@ -7990,6 +10745,11 @@
       </c>
     </row>
     <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B578" t="inlineStr">
         <is>
           <t>Nogales</t>
@@ -8003,6 +10763,11 @@
       </c>
     </row>
     <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B579" t="inlineStr">
         <is>
           <t>San Luis Río Colorado</t>
@@ -8016,6 +10781,11 @@
       </c>
     </row>
     <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B580" t="inlineStr">
         <is>
           <t>Total</t>
@@ -8047,6 +10817,11 @@
       </c>
     </row>
     <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B582" t="inlineStr">
         <is>
           <t>Cárdenas</t>
@@ -8060,6 +10835,11 @@
       </c>
     </row>
     <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B583" t="inlineStr">
         <is>
           <t>Centro</t>
@@ -8073,6 +10853,11 @@
       </c>
     </row>
     <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B584" t="inlineStr">
         <is>
           <t>Comalcalco</t>
@@ -8086,6 +10871,11 @@
       </c>
     </row>
     <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B585" t="inlineStr">
         <is>
           <t>Cunduacán</t>
@@ -8099,6 +10889,11 @@
       </c>
     </row>
     <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B586" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -8112,6 +10907,11 @@
       </c>
     </row>
     <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B587" t="inlineStr">
         <is>
           <t>Huimanguillo</t>
@@ -8125,6 +10925,11 @@
       </c>
     </row>
     <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B588" t="inlineStr">
         <is>
           <t>Jonuta</t>
@@ -8138,6 +10943,11 @@
       </c>
     </row>
     <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B589" t="inlineStr">
         <is>
           <t>Macuspana</t>
@@ -8151,6 +10961,11 @@
       </c>
     </row>
     <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B590" t="inlineStr">
         <is>
           <t>Paraíso</t>
@@ -8164,6 +10979,11 @@
       </c>
     </row>
     <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B591" t="inlineStr">
         <is>
           <t>Tacotalpa</t>
@@ -8177,6 +10997,11 @@
       </c>
     </row>
     <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B592" t="inlineStr">
         <is>
           <t>Tenosique</t>
@@ -8190,6 +11015,11 @@
       </c>
     </row>
     <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B593" t="inlineStr">
         <is>
           <t>Total</t>
@@ -8221,6 +11051,11 @@
       </c>
     </row>
     <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B595" t="inlineStr">
         <is>
           <t>Altamira</t>
@@ -8234,6 +11069,11 @@
       </c>
     </row>
     <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B596" t="inlineStr">
         <is>
           <t>Bustamante</t>
@@ -8247,6 +11087,11 @@
       </c>
     </row>
     <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B597" t="inlineStr">
         <is>
           <t>Casas</t>
@@ -8260,6 +11105,11 @@
       </c>
     </row>
     <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B598" t="inlineStr">
         <is>
           <t>Ciudad Madero</t>
@@ -8273,6 +11123,11 @@
       </c>
     </row>
     <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B599" t="inlineStr">
         <is>
           <t>El Mante</t>
@@ -8286,6 +11141,11 @@
       </c>
     </row>
     <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B600" t="inlineStr">
         <is>
           <t>González</t>
@@ -8299,6 +11159,11 @@
       </c>
     </row>
     <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B601" t="inlineStr">
         <is>
           <t>Gustavo Díaz Ordaz</t>
@@ -8312,6 +11177,11 @@
       </c>
     </row>
     <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B602" t="inlineStr">
         <is>
           <t>Llera</t>
@@ -8325,6 +11195,11 @@
       </c>
     </row>
     <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B603" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -8338,6 +11213,11 @@
       </c>
     </row>
     <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B604" t="inlineStr">
         <is>
           <t>Mier</t>
@@ -8351,6 +11231,11 @@
       </c>
     </row>
     <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B605" t="inlineStr">
         <is>
           <t>Miguel Alemán</t>
@@ -8364,6 +11249,11 @@
       </c>
     </row>
     <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B606" t="inlineStr">
         <is>
           <t>Nuevo Laredo</t>
@@ -8377,6 +11267,11 @@
       </c>
     </row>
     <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B607" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -8390,6 +11285,11 @@
       </c>
     </row>
     <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B608" t="inlineStr">
         <is>
           <t>Padilla</t>
@@ -8403,6 +11303,11 @@
       </c>
     </row>
     <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B609" t="inlineStr">
         <is>
           <t>Reynosa</t>
@@ -8416,6 +11321,11 @@
       </c>
     </row>
     <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B610" t="inlineStr">
         <is>
           <t>Río Bravo</t>
@@ -8429,6 +11339,11 @@
       </c>
     </row>
     <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B611" t="inlineStr">
         <is>
           <t>San Fernando</t>
@@ -8442,6 +11357,11 @@
       </c>
     </row>
     <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B612" t="inlineStr">
         <is>
           <t>Tampico</t>
@@ -8455,6 +11375,11 @@
       </c>
     </row>
     <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B613" t="inlineStr">
         <is>
           <t>Tula</t>
@@ -8468,6 +11393,11 @@
       </c>
     </row>
     <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B614" t="inlineStr">
         <is>
           <t>Valle Hermoso</t>
@@ -8481,6 +11411,11 @@
       </c>
     </row>
     <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B615" t="inlineStr">
         <is>
           <t>Victoria</t>
@@ -8494,6 +11429,11 @@
       </c>
     </row>
     <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B616" t="inlineStr">
         <is>
           <t>Villagrán</t>
@@ -8507,6 +11447,11 @@
       </c>
     </row>
     <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B617" t="inlineStr">
         <is>
           <t>Total</t>
@@ -8538,6 +11483,11 @@
       </c>
     </row>
     <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B619" t="inlineStr">
         <is>
           <t>El Carmen Tequexquitla</t>
@@ -8551,6 +11501,11 @@
       </c>
     </row>
     <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B620" t="inlineStr">
         <is>
           <t>Huamantla</t>
@@ -8564,9 +11519,14 @@
       </c>
     </row>
     <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Ixtacuixtla de Mariano Matamoros</t>
+          <t>Ixtacuixtla De Mariano Matamoros</t>
         </is>
       </c>
       <c r="C621">
@@ -8577,6 +11537,11 @@
       </c>
     </row>
     <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B622" t="inlineStr">
         <is>
           <t>Panotla</t>
@@ -8590,6 +11555,11 @@
       </c>
     </row>
     <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B623" t="inlineStr">
         <is>
           <t>Terrenate</t>
@@ -8603,6 +11573,11 @@
       </c>
     </row>
     <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B624" t="inlineStr">
         <is>
           <t>Tetlatlahuca</t>
@@ -8616,6 +11591,11 @@
       </c>
     </row>
     <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B625" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -8629,6 +11609,11 @@
       </c>
     </row>
     <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B626" t="inlineStr">
         <is>
           <t>Tlaxco</t>
@@ -8642,6 +11627,11 @@
       </c>
     </row>
     <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B627" t="inlineStr">
         <is>
           <t>Xaloztoc</t>
@@ -8655,6 +11645,11 @@
       </c>
     </row>
     <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B628" t="inlineStr">
         <is>
           <t>Total</t>
@@ -8686,6 +11681,11 @@
       </c>
     </row>
     <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B630" t="inlineStr">
         <is>
           <t>Actopan</t>
@@ -8699,6 +11699,11 @@
       </c>
     </row>
     <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B631" t="inlineStr">
         <is>
           <t>Acula</t>
@@ -8712,6 +11717,11 @@
       </c>
     </row>
     <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B632" t="inlineStr">
         <is>
           <t>Altotonga</t>
@@ -8725,6 +11735,11 @@
       </c>
     </row>
     <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B633" t="inlineStr">
         <is>
           <t>Alvarado</t>
@@ -8738,9 +11753,14 @@
       </c>
     </row>
     <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Amatlán de los Reyes</t>
+          <t>Amatlán De Los Reyes</t>
         </is>
       </c>
       <c r="C634">
@@ -8751,6 +11771,11 @@
       </c>
     </row>
     <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B635" t="inlineStr">
         <is>
           <t>Angel R. Cabada</t>
@@ -8764,6 +11789,11 @@
       </c>
     </row>
     <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B636" t="inlineStr">
         <is>
           <t>Astacinga</t>
@@ -8777,6 +11807,11 @@
       </c>
     </row>
     <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B637" t="inlineStr">
         <is>
           <t>Atlahuilco</t>
@@ -8790,6 +11825,11 @@
       </c>
     </row>
     <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B638" t="inlineStr">
         <is>
           <t>Atzalan</t>
@@ -8803,6 +11843,11 @@
       </c>
     </row>
     <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B639" t="inlineStr">
         <is>
           <t>Ayahualulco</t>
@@ -8816,6 +11861,11 @@
       </c>
     </row>
     <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B640" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -8829,9 +11879,14 @@
       </c>
     </row>
     <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Boca del Río</t>
+          <t>Boca Del Río</t>
         </is>
       </c>
       <c r="C641">
@@ -8842,6 +11897,11 @@
       </c>
     </row>
     <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B642" t="inlineStr">
         <is>
           <t>Catemaco</t>
@@ -8855,6 +11915,11 @@
       </c>
     </row>
     <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B643" t="inlineStr">
         <is>
           <t>Chacaltianguis</t>
@@ -8868,6 +11933,11 @@
       </c>
     </row>
     <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B644" t="inlineStr">
         <is>
           <t>Chicontepec</t>
@@ -8881,6 +11951,11 @@
       </c>
     </row>
     <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B645" t="inlineStr">
         <is>
           <t>Chumatlán</t>
@@ -8894,6 +11969,11 @@
       </c>
     </row>
     <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B646" t="inlineStr">
         <is>
           <t>Coatzacoalcos</t>
@@ -8907,6 +11987,11 @@
       </c>
     </row>
     <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B647" t="inlineStr">
         <is>
           <t>Colipa</t>
@@ -8920,6 +12005,11 @@
       </c>
     </row>
     <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B648" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -8933,9 +12023,14 @@
       </c>
     </row>
     <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Cosamaloapan de Carpio</t>
+          <t>Cosamaloapan De Carpio</t>
         </is>
       </c>
       <c r="C649">
@@ -8946,9 +12041,14 @@
       </c>
     </row>
     <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Cosautlán de Carvajal</t>
+          <t>Cosautlán De Carvajal</t>
         </is>
       </c>
       <c r="C650">
@@ -8959,6 +12059,11 @@
       </c>
     </row>
     <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B651" t="inlineStr">
         <is>
           <t>Coscomatepec</t>
@@ -8972,6 +12077,11 @@
       </c>
     </row>
     <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B652" t="inlineStr">
         <is>
           <t>Cotaxtla</t>
@@ -8985,6 +12095,11 @@
       </c>
     </row>
     <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B653" t="inlineStr">
         <is>
           <t>Coyutla</t>
@@ -8998,6 +12113,11 @@
       </c>
     </row>
     <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B654" t="inlineStr">
         <is>
           <t>Cuitláhuac</t>
@@ -9011,6 +12131,11 @@
       </c>
     </row>
     <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B655" t="inlineStr">
         <is>
           <t>Fortín</t>
@@ -9024,6 +12149,11 @@
       </c>
     </row>
     <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B656" t="inlineStr">
         <is>
           <t>Gutiérrez Zamora</t>
@@ -9037,6 +12167,11 @@
       </c>
     </row>
     <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B657" t="inlineStr">
         <is>
           <t>Hidalgotitlán</t>
@@ -9050,6 +12185,11 @@
       </c>
     </row>
     <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B658" t="inlineStr">
         <is>
           <t>Huatusco</t>
@@ -9063,9 +12203,14 @@
       </c>
     </row>
     <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C659">
@@ -9076,6 +12221,11 @@
       </c>
     </row>
     <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B660" t="inlineStr">
         <is>
           <t>Isla</t>
@@ -9089,9 +12239,14 @@
       </c>
     </row>
     <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Ixhuatlán de Madero</t>
+          <t>Ixhuatlán De Madero</t>
         </is>
       </c>
       <c r="C661">
@@ -9102,9 +12257,14 @@
       </c>
     </row>
     <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Ixhuatlán del Sureste</t>
+          <t>Ixhuatlán Del Sureste</t>
         </is>
       </c>
       <c r="C662">
@@ -9115,6 +12275,11 @@
       </c>
     </row>
     <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B663" t="inlineStr">
         <is>
           <t>Jalacingo</t>
@@ -9128,6 +12293,11 @@
       </c>
     </row>
     <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B664" t="inlineStr">
         <is>
           <t>Jalcomulco</t>
@@ -9141,6 +12311,11 @@
       </c>
     </row>
     <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B665" t="inlineStr">
         <is>
           <t>Jamapa</t>
@@ -9154,6 +12329,11 @@
       </c>
     </row>
     <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B666" t="inlineStr">
         <is>
           <t>Jesús Carranza</t>
@@ -9167,6 +12347,11 @@
       </c>
     </row>
     <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B667" t="inlineStr">
         <is>
           <t>Juan Rodríguez Clara</t>
@@ -9180,6 +12365,11 @@
       </c>
     </row>
     <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B668" t="inlineStr">
         <is>
           <t>Las Choapas</t>
@@ -9193,6 +12383,11 @@
       </c>
     </row>
     <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B669" t="inlineStr">
         <is>
           <t>Las Minas</t>
@@ -9206,9 +12401,14 @@
       </c>
     </row>
     <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Lerdo de Tejada</t>
+          <t>Lerdo De Tejada</t>
         </is>
       </c>
       <c r="C670">
@@ -9219,9 +12419,14 @@
       </c>
     </row>
     <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C671">
@@ -9232,6 +12437,11 @@
       </c>
     </row>
     <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B672" t="inlineStr">
         <is>
           <t>Minatitlán</t>
@@ -9245,6 +12455,11 @@
       </c>
     </row>
     <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B673" t="inlineStr">
         <is>
           <t>Misantla</t>
@@ -9258,6 +12473,11 @@
       </c>
     </row>
     <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B674" t="inlineStr">
         <is>
           <t>Moloacán</t>
@@ -9271,6 +12491,11 @@
       </c>
     </row>
     <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B675" t="inlineStr">
         <is>
           <t>Oluta</t>
@@ -9284,6 +12509,11 @@
       </c>
     </row>
     <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B676" t="inlineStr">
         <is>
           <t>Omealca</t>
@@ -9297,6 +12527,11 @@
       </c>
     </row>
     <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B677" t="inlineStr">
         <is>
           <t>Orizaba</t>
@@ -9310,9 +12545,14 @@
       </c>
     </row>
     <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Ozuluama de Mascareñas</t>
+          <t>Ozuluama De Mascareñas</t>
         </is>
       </c>
       <c r="C678">
@@ -9323,6 +12563,11 @@
       </c>
     </row>
     <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B679" t="inlineStr">
         <is>
           <t>Pánuco</t>
@@ -9336,6 +12581,11 @@
       </c>
     </row>
     <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B680" t="inlineStr">
         <is>
           <t>Papantla</t>
@@ -9349,6 +12599,11 @@
       </c>
     </row>
     <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B681" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -9362,9 +12617,14 @@
       </c>
     </row>
     <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Poza Rica de Hidalgo</t>
+          <t>Poza Rica De Hidalgo</t>
         </is>
       </c>
       <c r="C682">
@@ -9375,6 +12635,11 @@
       </c>
     </row>
     <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B683" t="inlineStr">
         <is>
           <t>Río Blanco</t>
@@ -9388,6 +12653,11 @@
       </c>
     </row>
     <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B684" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -9401,6 +12671,11 @@
       </c>
     </row>
     <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B685" t="inlineStr">
         <is>
           <t>San Juan Evangelista</t>
@@ -9414,6 +12689,11 @@
       </c>
     </row>
     <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B686" t="inlineStr">
         <is>
           <t>Santiago Tuxtla</t>
@@ -9427,9 +12707,14 @@
       </c>
     </row>
     <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Sayula de Alemán</t>
+          <t>Sayula De Alemán</t>
         </is>
       </c>
       <c r="C687">
@@ -9440,6 +12725,11 @@
       </c>
     </row>
     <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B688" t="inlineStr">
         <is>
           <t>Soconusco</t>
@@ -9453,6 +12743,11 @@
       </c>
     </row>
     <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B689" t="inlineStr">
         <is>
           <t>Tamiahua</t>
@@ -9466,6 +12761,11 @@
       </c>
     </row>
     <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B690" t="inlineStr">
         <is>
           <t>Tantoyuca</t>
@@ -9479,6 +12779,11 @@
       </c>
     </row>
     <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B691" t="inlineStr">
         <is>
           <t>Tecolutla</t>
@@ -9492,6 +12797,11 @@
       </c>
     </row>
     <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B692" t="inlineStr">
         <is>
           <t>Álamo Temapache</t>
@@ -9505,6 +12815,11 @@
       </c>
     </row>
     <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B693" t="inlineStr">
         <is>
           <t>Tempoal</t>
@@ -9518,6 +12833,11 @@
       </c>
     </row>
     <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B694" t="inlineStr">
         <is>
           <t>Tenochtitlán</t>
@@ -9531,6 +12851,11 @@
       </c>
     </row>
     <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B695" t="inlineStr">
         <is>
           <t>Teocelo</t>
@@ -9544,6 +12869,11 @@
       </c>
     </row>
     <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B696" t="inlineStr">
         <is>
           <t>Texistepec</t>
@@ -9557,6 +12887,11 @@
       </c>
     </row>
     <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B697" t="inlineStr">
         <is>
           <t>Tezonapa</t>
@@ -9570,6 +12905,11 @@
       </c>
     </row>
     <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B698" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -9583,6 +12923,11 @@
       </c>
     </row>
     <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B699" t="inlineStr">
         <is>
           <t>Tihuatlán</t>
@@ -9596,6 +12941,11 @@
       </c>
     </row>
     <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B700" t="inlineStr">
         <is>
           <t>Tlacotalpan</t>
@@ -9609,6 +12959,11 @@
       </c>
     </row>
     <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B701" t="inlineStr">
         <is>
           <t>Tlalixcoyan</t>
@@ -9622,6 +12977,11 @@
       </c>
     </row>
     <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B702" t="inlineStr">
         <is>
           <t>Tlaltetela</t>
@@ -9635,6 +12995,11 @@
       </c>
     </row>
     <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B703" t="inlineStr">
         <is>
           <t>Tlapacoyan</t>
@@ -9648,6 +13013,11 @@
       </c>
     </row>
     <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B704" t="inlineStr">
         <is>
           <t>Tonayán</t>
@@ -9661,6 +13031,11 @@
       </c>
     </row>
     <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B705" t="inlineStr">
         <is>
           <t>Totutla</t>
@@ -9674,6 +13049,11 @@
       </c>
     </row>
     <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B706" t="inlineStr">
         <is>
           <t>Tres Valles</t>
@@ -9687,6 +13067,11 @@
       </c>
     </row>
     <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B707" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -9700,6 +13085,11 @@
       </c>
     </row>
     <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B708" t="inlineStr">
         <is>
           <t>Uxpanapa</t>
@@ -9713,6 +13103,11 @@
       </c>
     </row>
     <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B709" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -9726,6 +13121,11 @@
       </c>
     </row>
     <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B710" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -9739,6 +13139,11 @@
       </c>
     </row>
     <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B711" t="inlineStr">
         <is>
           <t>Zentla</t>
@@ -9752,6 +13157,11 @@
       </c>
     </row>
     <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B712" t="inlineStr">
         <is>
           <t>Zongolica</t>
@@ -9765,6 +13175,11 @@
       </c>
     </row>
     <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B713" t="inlineStr">
         <is>
           <t>Total</t>
@@ -9796,6 +13211,11 @@
       </c>
     </row>
     <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B715" t="inlineStr">
         <is>
           <t>Mérida</t>
@@ -9809,6 +13229,11 @@
       </c>
     </row>
     <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B716" t="inlineStr">
         <is>
           <t>Sacalum</t>
@@ -9822,6 +13247,11 @@
       </c>
     </row>
     <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B717" t="inlineStr">
         <is>
           <t>Tahmek</t>
@@ -9835,6 +13265,11 @@
       </c>
     </row>
     <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B718" t="inlineStr">
         <is>
           <t>Total</t>
@@ -9866,6 +13301,11 @@
       </c>
     </row>
     <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B720" t="inlineStr">
         <is>
           <t>Chalchihuites</t>
@@ -9879,6 +13319,11 @@
       </c>
     </row>
     <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B721" t="inlineStr">
         <is>
           <t>El Salvador</t>
@@ -9892,6 +13337,11 @@
       </c>
     </row>
     <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B722" t="inlineStr">
         <is>
           <t>Fresnillo</t>
@@ -9905,6 +13355,11 @@
       </c>
     </row>
     <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B723" t="inlineStr">
         <is>
           <t>General Pánfilo Natera</t>
@@ -9918,6 +13373,11 @@
       </c>
     </row>
     <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B724" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -9931,6 +13391,11 @@
       </c>
     </row>
     <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B725" t="inlineStr">
         <is>
           <t>Jerez</t>
@@ -9944,6 +13409,11 @@
       </c>
     </row>
     <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B726" t="inlineStr">
         <is>
           <t>Juan Aldama</t>
@@ -9957,6 +13427,11 @@
       </c>
     </row>
     <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B727" t="inlineStr">
         <is>
           <t>Juchipila</t>
@@ -9970,6 +13445,11 @@
       </c>
     </row>
     <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B728" t="inlineStr">
         <is>
           <t>Mazapil</t>
@@ -9983,6 +13463,11 @@
       </c>
     </row>
     <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B729" t="inlineStr">
         <is>
           <t>Miguel Auza</t>
@@ -9996,9 +13481,14 @@
       </c>
     </row>
     <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Nochistlán de Mejía</t>
+          <t>Nochistlán De Mejía</t>
         </is>
       </c>
       <c r="C730">
@@ -10009,9 +13499,14 @@
       </c>
     </row>
     <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Noria de Ángeles</t>
+          <t>Noria De Ángeles</t>
         </is>
       </c>
       <c r="C731">
@@ -10022,6 +13517,11 @@
       </c>
     </row>
     <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B732" t="inlineStr">
         <is>
           <t>Ojocaliente</t>
@@ -10035,6 +13535,11 @@
       </c>
     </row>
     <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B733" t="inlineStr">
         <is>
           <t>Pinos</t>
@@ -10048,6 +13553,11 @@
       </c>
     </row>
     <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B734" t="inlineStr">
         <is>
           <t>Río Grande</t>
@@ -10061,6 +13571,11 @@
       </c>
     </row>
     <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B735" t="inlineStr">
         <is>
           <t>Sain Alto</t>
@@ -10074,6 +13589,11 @@
       </c>
     </row>
     <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B736" t="inlineStr">
         <is>
           <t>Sombrerete</t>
@@ -10087,6 +13607,11 @@
       </c>
     </row>
     <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B737" t="inlineStr">
         <is>
           <t>Tepechitlán</t>
@@ -10100,9 +13625,14 @@
       </c>
     </row>
     <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Tlaltenango de Sánchez Román</t>
+          <t>Tlaltenango De Sánchez Román</t>
         </is>
       </c>
       <c r="C738">
@@ -10113,6 +13643,11 @@
       </c>
     </row>
     <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B739" t="inlineStr">
         <is>
           <t>Villa García</t>
@@ -10126,6 +13661,11 @@
       </c>
     </row>
     <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B740" t="inlineStr">
         <is>
           <t>Villa González Ortega</t>
@@ -10139,6 +13679,11 @@
       </c>
     </row>
     <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B741" t="inlineStr">
         <is>
           <t>Villa Hidalgo</t>
@@ -10152,6 +13697,11 @@
       </c>
     </row>
     <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B742" t="inlineStr">
         <is>
           <t>Zacatecas</t>
@@ -10165,6 +13715,11 @@
       </c>
     </row>
     <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B743" t="inlineStr">
         <is>
           <t>Total</t>
@@ -10188,41 +13743,6 @@
       </c>
       <c r="D744">
         <v>1</v>
-      </c>
-    </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 566,547</t>
-        </is>
-      </c>
-    </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="749">
-      <c r="A749" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="750">
-      <c r="A750" t="inlineStr">
-        <is>
-          <t>Mayo de 2023</t>
-        </is>
       </c>
     </row>
   </sheetData>
